--- a/data/trans_orig/IP16B08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B08-Habitat-trans_orig.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
